--- a/UnityTableTool/Data/ValidationExamples/05_TABLE_MERGE_ERROR_Test.xlsx
+++ b/UnityTableTool/Data/ValidationExamples/05_TABLE_MERGE_ERROR_Test.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\ValidationExamples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\Data\ValidationExamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25320" windowHeight="17175"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="TABLE_MERGE_ERROR_Test" sheetId="1" r:id="rId1"/>
@@ -571,7 +571,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1203,7 +1203,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
     <col min="3" max="4" width="16" customWidth="1"/>
